--- a/XLibur.Tests/Resource/Examples/Ranges/SortExample.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/SortExample.xlsx
@@ -21,30 +21,30 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
+    <x:t>B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>a</x:t>
+  </x:si>
+  <x:si>
+    <x:t>b</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Column1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Column2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Column3</x:t>
+  </x:si>
+  <x:si>
     <x:t>.Sort("Column2, Column3 Desc, Column1 ASC") = Sort table Top to Bottom, Col 2 Asc, Col 3 Desc, Col 1 Asc, Ignore Blanks, Ignore Case</x:t>
   </x:si>
   <x:si>
-    <x:t>Column1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Column2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Column3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>b</x:t>
-  </x:si>
-  <x:si>
-    <x:t>a</x:t>
-  </x:si>
-  <x:si>
     <x:t>.SortLeftToRight() = Sort Range Left to Right, Ascendingly, Ignore Blanks, Ignore Case</x:t>
   </x:si>
   <x:si>
@@ -60,10 +60,10 @@
     <x:t>.Sort("2, 1 DESC", XLSortOrder.Ascending, true) = Sort Range Top to Bottom, Col 2 Asc, Col 1 Desc, Ignore Blanks, Match Case</x:t>
   </x:si>
   <x:si>
+    <x:t>c</x:t>
+  </x:si>
+  <x:si>
     <x:t>.Sort(XLSortOrder.Descending, true) = Sort Range Top to Bottom, Descendingly, Ignore Blanks, Match Case</x:t>
-  </x:si>
-  <x:si>
-    <x:t>c</x:t>
   </x:si>
   <x:si>
     <x:t>.Sort() = Sort Range Top to Bottom, Ascendingly, Ignore Blanks, Ignore Case</x:t>
@@ -548,171 +548,171 @@
   <x:sheetData>
     <x:row r="1" spans="1:8">
       <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8">
       <x:c r="A3" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
       <x:c r="A4" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B4" s="2"/>
       <x:c r="C4" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H4" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
       <x:c r="A5" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C5" s="4"/>
       <x:c r="F5" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
       <x:c r="A6" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F6" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G6" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:8">
       <x:c r="A7" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F7" s="8"/>
       <x:c r="G7" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H7" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:8">
       <x:c r="A8" s="8"/>
       <x:c r="B8" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C8" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F8" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:8">
       <x:c r="A9" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F9" s="9" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G9" s="9" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H9" s="9"/>
     </x:row>
     <x:row r="10" spans="1:8">
       <x:c r="A10" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F10" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G10" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H10" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:8">
       <x:c r="A11" s="9" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B11" s="9" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C11" s="9"/>
       <x:c r="F11" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G11" s="2"/>
       <x:c r="H11" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -741,142 +741,142 @@
     </x:row>
     <x:row r="3" spans="1:8">
       <x:c r="A3" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D3" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3" s="8"/>
       <x:c r="F3" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G3" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H3" s="9" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
       <x:c r="A4" s="2"/>
       <x:c r="B4" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E4" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G4" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="9" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
       <x:c r="A5" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="4"/>
       <x:c r="C5" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E5" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F5" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G5" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="9"/>
     </x:row>
     <x:row r="8" spans="1:8">
       <x:c r="A8" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B8" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F8" s="9" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G8" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="8"/>
     </x:row>
     <x:row r="9" spans="1:8">
       <x:c r="A9" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E9" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F9" s="9" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G9" s="2"/>
       <x:c r="H9" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
       <x:c r="A10" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D10" s="4"/>
       <x:c r="E10" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F10" s="9"/>
       <x:c r="G10" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H10" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -916,145 +916,145 @@
     </x:row>
     <x:row r="5" spans="1:8">
       <x:c r="A5" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B5" s="2"/>
       <x:c r="C5" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F5" s="8"/>
       <x:c r="G5" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H5" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
       <x:c r="A6" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="4"/>
       <x:c r="F6" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G6" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:8">
       <x:c r="A7" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C7" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F7" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G7" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H7" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:8">
       <x:c r="A8" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:8">
       <x:c r="A9" s="8"/>
       <x:c r="B9" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C9" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F9" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H9" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
       <x:c r="A10" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F10" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H10" s="4"/>
     </x:row>
     <x:row r="11" spans="1:8">
       <x:c r="A11" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B11" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F11" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G11" s="2"/>
       <x:c r="H11" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:8">
       <x:c r="A12" s="9" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B12" s="9" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C12" s="9"/>
       <x:c r="F12" s="9" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G12" s="9" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H12" s="9"/>
     </x:row>
@@ -1085,146 +1085,146 @@
     </x:row>
     <x:row r="3" spans="1:8">
       <x:c r="A3" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F3" s="9" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3" s="9" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H3" s="9"/>
     </x:row>
     <x:row r="4" spans="1:8">
       <x:c r="A4" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="4"/>
       <x:c r="F4" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G4" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:8">
       <x:c r="A5" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F5" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G5" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H5" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
       <x:c r="A6" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F6" s="8"/>
       <x:c r="G6" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:8">
       <x:c r="A7" s="8"/>
       <x:c r="B7" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F7" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H7" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:8">
       <x:c r="A8" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:8">
       <x:c r="A9" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B9" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F9" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G9" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
       <x:c r="A10" s="9" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B10" s="9" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C10" s="9"/>
       <x:c r="F10" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G10" s="2"/>
       <x:c r="H10" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1249,62 +1249,62 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="9" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="5"/>
       <x:c r="D6" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="8"/>
       <x:c r="D7" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D8" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="5"/>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="9" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D10" s="8"/>
     </x:row>
@@ -1335,146 +1335,146 @@
     </x:row>
     <x:row r="3" spans="1:8">
       <x:c r="A3" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F3" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G3" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H3" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
       <x:c r="A4" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="4"/>
       <x:c r="F4" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G4" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
       <x:c r="A5" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F5" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
       <x:c r="A6" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F6" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:8">
       <x:c r="A7" s="8"/>
       <x:c r="B7" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F7" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G7" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H7" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:8">
       <x:c r="A8" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F8" s="9" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G8" s="9" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H8" s="9"/>
     </x:row>
     <x:row r="9" spans="1:8">
       <x:c r="A9" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B9" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F9" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G9" s="2"/>
       <x:c r="H9" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
       <x:c r="A10" s="9" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B10" s="9" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C10" s="9"/>
       <x:c r="F10" s="8"/>
       <x:c r="G10" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H10" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/XLibur.Tests/Resource/Examples/Ranges/SortExample.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/SortExample.xlsx
@@ -537,13 +537,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:H11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="6" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="1" max="6" width="9.140625"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
@@ -552,22 +549,22 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="A3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="C3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
+      <x:c r="F3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
+      <x:c r="G3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H3" s="0" t="s">
+      <x:c r="H3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -716,10 +713,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId10"/>
   </x:tableParts>
@@ -728,9 +722,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:H10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -880,23 +871,16 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:H12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="6" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="1" max="6" width="9.140625"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
@@ -1059,23 +1043,16 @@
       <x:c r="H12" s="9"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:H10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="6" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="1" max="6" width="9.140625"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
@@ -1228,23 +1205,16 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:D10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="4" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="1" max="4" width="9.140625"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -1309,23 +1279,16 @@
       <x:c r="D10" s="8"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:H10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="6" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="1" max="6" width="9.140625"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
@@ -1478,10 +1441,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Ranges/SortExample.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/SortExample.xlsx
@@ -540,7 +540,7 @@
   <x:dimension ref="A1:H11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="6" width="9.140625"/>
+    <x:col min="1" max="6" width="9.144286"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
@@ -880,7 +880,7 @@
   <x:dimension ref="A1:H12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="6" width="9.140625"/>
+    <x:col min="1" max="6" width="9.144286"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
@@ -1052,7 +1052,7 @@
   <x:dimension ref="A1:H10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="6" width="9.140625"/>
+    <x:col min="1" max="6" width="9.144286"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
@@ -1214,7 +1214,7 @@
   <x:dimension ref="A1:D10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="4" width="9.140625"/>
+    <x:col min="1" max="4" width="9.144286"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -1288,7 +1288,7 @@
   <x:dimension ref="A1:H10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="6" width="9.140625"/>
+    <x:col min="1" max="6" width="9.144286"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
